--- a/CodeVS/data/output/barge_schedule_Export_test.xlsx
+++ b/CodeVS/data/output/barge_schedule_Export_test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="86">
   <si>
     <t>barge</t>
   </si>
@@ -133,18 +133,18 @@
     <t>Barge ID: B_040, Name: จากัวร์ 11, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:10:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
+    <t>Barge ID: B_095, Name: ปอร์เช่ 24, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_088, Name: ปอร์เช่ 16, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
     <t>Barge ID: B_041, Name: จากัวร์ 12, LOAD: 3500, Capacity: 3500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_013, Name: SP 57, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_095, Name: ปอร์เช่ 24, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_088, Name: ปอร์เช่ 16, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
     <t>Barge ID: B_026, Name: SPI 06, LOAD: 2700, Capacity: 2700, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-31 06:10:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
@@ -166,75 +166,75 @@
     <t>Barge ID: B_004, Name: SP 30, LOAD: 2100, Capacity: 2100, Location: (28.8232, 201.183), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
+    <t>Barge ID: B_102, Name: เอาดี้ 07, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-15 06:25:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_063, Name: จากัวร์ 41, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:00:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_071, Name: จากัวร์ 50, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_022, Name: SPI 02, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_094, Name: ปอร์เช่ 23, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_020, Name: SP 77, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-18 08:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_068, Name: จากัวร์ 46, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_083, Name: ปอร์เช่ 06, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_027, Name: SPI 09, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_099, Name: เอาดี้ 03, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-21 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_023, Name: SPI 03, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_028, Name: SPI 12, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_033, Name: จากัวร์ 02, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_017, Name: SP 65, LOAD: 2300, Capacity: 2300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_024, Name: SPI 04, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:25:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
+    <t>Barge ID: B_016, Name: SP 64, LOAD: 1500, Capacity: 2300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 04:55:00, Water Status: WaterBody.SEA</t>
+  </si>
+  <si>
     <t>Barge ID: B_101, Name: เอาดี้ 05, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_062, Name: จากัวร์ 40, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-06 08:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_068, Name: จากัวร์ 46, LOAD: 2500, Capacity: 2500, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 07:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_027, Name: SPI 09, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_097, Name: เอาดี้ 01, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-01 09:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_023, Name: SPI 03, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 08:10:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_022, Name: SPI 02, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 08:50:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_093, Name: ปอร์เช่ 21, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-03 08:40:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_034, Name: จากัวร์ 03, LOAD: 250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_028, Name: SPI 12, LOAD: 2900, Capacity: 2900, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-04 08:40:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_085, Name: ปอร์เช่ 09, LOAD: 50, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>Barge ID: B_081, Name: ปอร์เช่ 04, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 07:50:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
-    <t>Barge ID: B_020, Name: SP 77, LOAD: 2100, Capacity: 2100, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-18 08:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_033, Name: จากัวร์ 02, LOAD: 3250, Capacity: 3250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-17 07:30:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_017, Name: SP 65, LOAD: 2300, Capacity: 2300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-19 07:15:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_024, Name: SPI 04, LOAD: 2600, Capacity: 2600, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-16 10:25:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_016, Name: SP 64, LOAD: 1500, Capacity: 2300, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-28 04:55:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_102, Name: เอาดี้ 07, LOAD: 2750, Capacity: 2750, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-15 06:25:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_085, Name: ปอร์เช่ 09, LOAD: 50, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-20 09:00:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_083, Name: ปอร์เช่ 06, LOAD: 3150, Capacity: 3150, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-30 06:20:00, Water Status: WaterBody.SEA</t>
-  </si>
-  <si>
-    <t>Barge ID: B_050, Name: จากัวร์ 24, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-02-02 07:50:00, Water Status: WaterBody.SEA</t>
+    <t>Barge ID: B_047, Name: จากัวร์ 19, LOAD: 2250, Capacity: 2250, Location: (13.1885, 100.815), Setup Time: 20 mins, Ready Time: 2024-01-18 09:00:00, Water Status: WaterBody.SEA</t>
   </si>
   <si>
     <t>(datetime.datetime(2025, 11, 23, 17, 0, 57), datetime.datetime(2025, 12, 24, 17, 0, 57))</t>
   </si>
   <si>
+    <t>Order_51</t>
+  </si>
+  <si>
     <t>Order_50</t>
   </si>
   <si>
-    <t>Order_51</t>
-  </si>
-  <si>
     <t>Order_52</t>
   </si>
   <si>
@@ -259,19 +259,19 @@
     <t>SeaTB_07</t>
   </si>
   <si>
+    <t>RiverTB_08</t>
+  </si>
+  <si>
     <t>RiverTB_01</t>
   </si>
   <si>
     <t>RiverTB_09</t>
   </si>
   <si>
-    <t>RiverTB_08</t>
-  </si>
-  <si>
     <t>RiverTB_11</t>
   </si>
   <si>
-    <t>RiverTB_12</t>
+    <t>RiverTB_10</t>
   </si>
 </sst>
 </file>
@@ -629,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1300,7 +1300,7 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>3500</v>
+        <v>3150</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1320,7 +1320,7 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>2100</v>
+        <v>3150</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1340,7 +1340,7 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>3150</v>
+        <v>3500</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>72</v>
       </c>
       <c r="F36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1360,7 +1360,7 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B45">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="C45">
         <v>10230.12942275319</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B46">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="C46">
         <v>10230.12942275319</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B47">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="C47">
         <v>10228.98246237894</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B48">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="C48">
         <v>10228.98246237894</v>
@@ -1597,13 +1597,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="B49">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C49">
-        <v>10228.98246237894</v>
+        <v>10284.89209676953</v>
       </c>
       <c r="D49" t="s">
         <v>70</v>
@@ -1612,15 +1612,15 @@
         <v>73</v>
       </c>
       <c r="G49" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B50">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="C50">
         <v>10284.89209676953</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51">
         <v>2500</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="C52">
         <v>10284.89209676953</v>
@@ -1672,15 +1672,15 @@
         <v>73</v>
       </c>
       <c r="G52" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="C53">
         <v>10284.89209676953</v>
@@ -1692,15 +1692,15 @@
         <v>73</v>
       </c>
       <c r="G53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54">
-        <v>2750</v>
+        <v>2100</v>
       </c>
       <c r="C54">
         <v>10284.89209676953</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B55">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="C55">
         <v>10284.89209676953</v>
@@ -1732,15 +1732,15 @@
         <v>73</v>
       </c>
       <c r="G55" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B56">
-        <v>2600</v>
+        <v>3150</v>
       </c>
       <c r="C56">
         <v>10284.89209676953</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B57">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C57">
         <v>10284.89209676953</v>
@@ -1772,15 +1772,15 @@
         <v>73</v>
       </c>
       <c r="G57" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B58">
-        <v>250</v>
+        <v>2750</v>
       </c>
       <c r="C58">
         <v>10284.89209676953</v>
@@ -1792,15 +1792,15 @@
         <v>73</v>
       </c>
       <c r="G58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B59">
-        <v>2900</v>
+        <v>2600</v>
       </c>
       <c r="C59">
         <v>10284.89209676953</v>
@@ -1812,15 +1812,15 @@
         <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B60">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="C60">
         <v>10284.89209676953</v>
@@ -1832,35 +1832,35 @@
         <v>73</v>
       </c>
       <c r="G60" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61">
-        <v>2100</v>
+        <v>3250</v>
       </c>
       <c r="C61">
-        <v>10284.89209676953</v>
+        <v>0</v>
       </c>
       <c r="D61" t="s">
         <v>70</v>
       </c>
       <c r="E61" t="s">
-        <v>73</v>
-      </c>
-      <c r="G61" t="s">
-        <v>84</v>
+        <v>71</v>
+      </c>
+      <c r="F61" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62">
-        <v>3250</v>
+        <v>2300</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B63">
-        <v>2300</v>
+        <v>2600</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B64">
-        <v>2600</v>
+        <v>1500</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B65">
-        <v>1500</v>
+        <v>2750</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1929,18 +1929,18 @@
         <v>70</v>
       </c>
       <c r="E65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F65" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B66">
-        <v>2750</v>
+        <v>50</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B67">
-        <v>50</v>
+        <v>3150</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -1972,15 +1972,15 @@
         <v>72</v>
       </c>
       <c r="F67" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B68">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -1992,26 +1992,6 @@
         <v>72</v>
       </c>
       <c r="F68" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69">
-        <v>2250</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69" t="s">
-        <v>70</v>
-      </c>
-      <c r="E69" t="s">
-        <v>72</v>
-      </c>
-      <c r="F69" t="s">
         <v>79</v>
       </c>
     </row>
